--- a/Python/orders_from_order.xlsx
+++ b/Python/orders_from_order.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,94 +626,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TEENSY 4.1 H</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Teensy 4.1, USB, with header</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>45.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NKS 200 GR</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mains cable with safety plug, grey, 1.8 m</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DEBO RE 1CH HL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Developer boards - Relay module, 1 channel, 5 V, high/low</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LIM-P-82-70</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Temperature limiter, 70Â°C, NC, 250 V.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.98</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Python/orders_from_order.xlsx
+++ b/Python/orders_from_order.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,153 +422,158 @@
           <t>Supplier name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Reichelt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Product name</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Unit price</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MW RSP-320-24</t>
+          <t>Product name</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Switching power supply, PFC, 322 W, 24 V/13.4 A</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>Unit price</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Supplier Part Number</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SNT RS 15 12</t>
+          <t>MW RSP-320-24 | Switching power supply, PFC, 322 W, 24 V/13.4 A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Switching power supply, 15.6 W, 1.3 A, 12 V</t>
+          <t>Switching power supply, PFC, 322 W, 24 V/13.4 A</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>40.3471</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MW RSP-320-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LIM-P-82-60</t>
+          <t>SNT RS 15 12 | Switching power supply, 15.6 W, 1.3 A, 12 V</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Temperature limiter, 60Â°C, NC, 250 V.</t>
+          <t>Switching power supply, 15.6 W, 1.3 A, 12 V</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>6.1405</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SNT RS 15 12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LIM-P-82-80</t>
+          <t>LIM-P-82-60 | Temperature limiter, 60Â°C, NC, 250 V.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Temperature limiter, 80Â°C, NC, 250 V.</t>
+          <t>Temperature limiter, 60Â°C, NC, 250 V.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.0248</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LIM-P-82-60</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LIM-P-82-45</t>
+          <t>LIM-P-82-80 | Temperature limiter, 80Â°C, NC, 250 V.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Temperature limiter, 45Â°C, NC, 250 V.</t>
+          <t>Temperature limiter, 80Â°C, NC, 250 V.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.7273</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LIM-P-82-80</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEBO RELAIS2 2CH</t>
+          <t>LIM-P-82-45 | Temperature limiter, 45Â°C, NC, 250 V.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Developer boards - relay module, 2-channel, 5 V</t>
+          <t>Temperature limiter, 45Â°C, NC, 250 V.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -578,51 +583,93 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.5041</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LIM-P-82-45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SNT RS 15 5</t>
+          <t>DEBO RELAIS2 2CH | Developer boards - relay module, 2-channel, 5 V</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Switching power supply, 15 W, 3 A, 5 V</t>
+          <t>Developer boards - relay module, 2-channel, 5 V</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>2.5124</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DEBO RELAIS2 2CH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>SNT RS 15 5 | Switching power supply, 15 W, 3 A, 5 V</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Switching power supply, 15 W, 3 A, 5 V</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6.0165</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SNT RS 15 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SS-5GL | Micro Switch, 1x NO, Flat Lever</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Micro Switch, 1x NO, Flat Lever</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.5455</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>SS-5GL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Micro Switch, 1x NO, Flat Lever</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.66</t>
         </is>
       </c>
     </row>

--- a/Python/orders_from_order.xlsx
+++ b/Python/orders_from_order.xlsx
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Reichelt</t>
+          <t>Schäfter + Kirchhoff</t>
         </is>
       </c>
     </row>
@@ -460,174 +460,188 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MW RSP-320-24 | Switching power supply, PFC, 322 W, 24 V/13.4 A</t>
+          <t xml:space="preserve">60FC-4-M6.2-01 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Achromat </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Switching power supply, PFC, 322 W, 24 V/13.4 A</t>
+          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
+Achromat f'6.2 mm / NA 0.2 / AR 350 - 700 nm
+Inclined coupling axis, FC-APC connection</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.3471</t>
+          <t>428.9256</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MW RSP-320-24</t>
+          <t>60FC-4-M6.2-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SNT RS 15 12 | Switching power supply, 15.6 W, 1.3 A, 12 V</t>
+          <t>60FC-4-M8-10 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Monochromat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Switching power supply, 15.6 W, 1.3 A, 12 V</t>
+          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
+Monochromat f'8 mm / NA 0.23 / AR 630 - 1080 nm
+Inclined coupling axis, FC-APC connection</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6.1405</t>
+          <t>315.7025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SNT RS 15 12</t>
+          <t>60FC-4-M8-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LIM-P-82-60 | Temperature limiter, 60Â°C, NC, 250 V.</t>
+          <t>PMC-780-3-18E-500 | Old product code:, PMC-E-780-5.3-NA012-3-APC.EC-500-P, Singl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Temperature limiter, 60Â°C, NC, 250 V.</t>
+          <t>Old product code:
+PMC-E-780-5.3-NA012-3-APC.EC-500-P
+Single-mode fiber cable, 5.0 m long</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.0248</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LIM-P-82-60</t>
+          <t>PMC-780-3-18E-500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LIM-P-82-80 | Temperature limiter, 80Â°C, NC, 250 V.</t>
+          <t>PMC-780-3-18-500 | Old product code: -3.00%, PMC-780-5.3-NA012-3-APC-500-P, Sing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Temperature limiter, 80Â°C, NC, 250 V.</t>
+          <t>Old product code: -3.00%
+PMC-780-5.3-NA012-3-APC-500-P
+Single-mode fiber cable, 5.0 m long</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.7273</t>
+          <t>427.2727</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LIM-P-82-80</t>
+          <t>PMC-780-3-18-500</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LIM-P-82-45 | Temperature limiter, 45Â°C, NC, 250 V.</t>
+          <t>PMC-980-3-18E-500 | Old product code:, PMC-E-980-6.6-NA012-3-APC.EC-500-P, Singl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Temperature limiter, 45Â°C, NC, 250 V.</t>
+          <t>Old product code:
+PMC-E-980-6.6-NA012-3-APC.EC-500-P
+Single-mode fiber cable, 5.0 m long</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.5041</t>
+          <t>595.8678</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LIM-P-82-45</t>
+          <t>PMC-980-3-18E-500</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEBO RELAIS2 2CH | Developer boards - relay module, 2-channel, 5 V</t>
+          <t>PMC-460-3-18-500 | Old product code:, PMC-460-3.3-NA012-3-APC-500-P, Single-mode</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Developer boards - relay module, 2-channel, 5 V</t>
+          <t>Old product code:
+PMC-460-3.3-NA012-3-APC-500-P
+Single-mode fiber cable, 5.0 m long</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.5124</t>
+          <t>468.595</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DEBO RELAIS2 2CH</t>
+          <t>PMC-460-3-18-500</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SNT RS 15 5 | Switching power supply, 15 W, 3 A, 5 V</t>
+          <t xml:space="preserve">60FC-4-A6.2S-02 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Asphere </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Switching power supply, 15 W, 3 A, 5 V</t>
+          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
+Asphere f'6.2 mm / NA 0.3 / AR 600 - 1100 nm
+Inclined coupling axis, FC-APC connection</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -637,39 +651,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.0165</t>
+          <t>219.0083</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SNT RS 15 5</t>
+          <t>60FC-4-A6.2S-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SS-5GL | Micro Switch, 1x NO, Flat Lever</t>
+          <t xml:space="preserve">60FC-4-A6.2S-01 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Asphere </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micro Switch, 1x NO, Flat Lever</t>
+          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
+Asphere f'6.2 mm / NA 0.3 / AR 350 - 700 nm
+Inclined coupling axis, FC-APC connection</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.5455</t>
+          <t>371.9008</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SS-5GL</t>
+          <t>60FC-4-A6.2S-01</t>
         </is>
       </c>
     </row>

--- a/Python/orders_from_order.xlsx
+++ b/Python/orders_from_order.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Schäfter + Kirchhoff</t>
+          <t>Conrad</t>
         </is>
       </c>
     </row>
@@ -460,232 +460,81 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">60FC-4-M6.2-01 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Achromat </t>
+          <t>2557557-8J | VALUE USB 2.0 Kabel, USB A Male - Micro USB B Male, wit, 3 m</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
-Achromat f'6.2 mm / NA 0.2 / AR 350 - 700 nm
-Inclined coupling axis, FC-APC connection</t>
+          <t>VALUE USB 2.0 Kabel, USB A Male - Micro USB B Male, wit, 3 m</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>428.9256</t>
+          <t>2.8843</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>60FC-4-M6.2-01</t>
+          <t>2557557-8J</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>60FC-4-M8-10 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Monochromat</t>
+          <t>2269230-8J | PJRC Teensy41 Microcontroller Teensy 4.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
-Monochromat f'8 mm / NA 0.23 / AR 630 - 1080 nm
-Inclined coupling axis, FC-APC connection</t>
+          <t>PJRC Teensy41 Microcontroller Teensy 4.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>315.7025</t>
+          <t>36.3554</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60FC-4-M8-10</t>
+          <t>2269230-8J</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PMC-780-3-18E-500 | Old product code:, PMC-E-780-5.3-NA012-3-APC.EC-500-P, Singl</t>
+          <t>2445488-8J | Sygonix SY-4890976 Stekkerdoos 3-voudig Wit Randaarde stekker 1 stu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Old product code:
-PMC-E-780-5.3-NA012-3-APC.EC-500-P
-Single-mode fiber cable, 5.0 m long</t>
+          <t>Sygonix SY-4890976 Stekkerdoos 3-voudig Wit Randaarde stekker 1 stuk(s)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2.8843</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PMC-780-3-18E-500</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PMC-780-3-18-500 | Old product code: -3.00%, PMC-780-5.3-NA012-3-APC-500-P, Sing</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Old product code: -3.00%
-PMC-780-5.3-NA012-3-APC-500-P
-Single-mode fiber cable, 5.0 m long</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>427.2727</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PMC-780-3-18-500</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PMC-980-3-18E-500 | Old product code:, PMC-E-980-6.6-NA012-3-APC.EC-500-P, Singl</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Old product code:
-PMC-E-980-6.6-NA012-3-APC.EC-500-P
-Single-mode fiber cable, 5.0 m long</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>595.8678</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PMC-980-3-18E-500</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>PMC-460-3-18-500 | Old product code:, PMC-460-3.3-NA012-3-APC-500-P, Single-mode</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Old product code:
-PMC-460-3.3-NA012-3-APC-500-P
-Single-mode fiber cable, 5.0 m long</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>468.595</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PMC-460-3-18-500</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60FC-4-A6.2S-02 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Asphere </t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
-Asphere f'6.2 mm / NA 0.3 / AR 600 - 1100 nm
-Inclined coupling axis, FC-APC connection</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>219.0083</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>60FC-4-A6.2S-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60FC-4-A6.2S-01 | Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%, Asphere </t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Fiber Collimator, focusable, housing Ã˜ 12 mm -3.00%
-Asphere f'6.2 mm / NA 0.3 / AR 350 - 700 nm
-Inclined coupling axis, FC-APC connection</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>371.9008</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>60FC-4-A6.2S-01</t>
+          <t>2445488-8J</t>
         </is>
       </c>
     </row>

--- a/Python/orders_from_order.xlsx
+++ b/Python/orders_from_order.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Conrad</t>
+          <t>RS Components</t>
         </is>
       </c>
     </row>
@@ -460,66 +460,66 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2557557-8J | VALUE USB 2.0 Kabel, USB A Male - Micro USB B Male, wit, 3 m</t>
+          <t>8496128 | RS PRO France, Germany Mains Plug Black, 16A, Cable Rubber, 250 V, Scr</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VALUE USB 2.0 Kabel, USB A Male - Micro USB B Male, wit, 3 m</t>
+          <t>RS PRO France, Germany Mains Plug Black, 16A, Cable Rubber, 250 V, Screw</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.8843</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2557557-8J</t>
+          <t>8496128</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2269230-8J | PJRC Teensy41 Microcontroller Teensy 4.1</t>
+          <t>0425610 | Deutsch, DT Plastic Male 2 Way Wedge Lock for use with Automotive Conn</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PJRC Teensy41 Microcontroller Teensy 4.1</t>
+          <t>Deutsch, DT Plastic Male 2 Way Wedge Lock for use with Automotive Connectors</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>36.3554</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2269230-8J</t>
+          <t>0425610</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2445488-8J | Sygonix SY-4890976 Stekkerdoos 3-voudig Wit Randaarde stekker 1 stu</t>
+          <t>5132590 | RS PRO Insulated Crimp Bootlace Ferrule, 8 mm Pin Length, 1.5 mm Pin D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sygonix SY-4890976 Stekkerdoos 3-voudig Wit Randaarde stekker 1 stuk(s)</t>
+          <t>RS PRO Insulated Crimp Bootlace Ferrule, 8 mm Pin Length, 1.5 mm Pin Diameter, Grey from 18 AWG to 18 AWG Wire Size</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -529,12 +529,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.8843</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2445488-8J</t>
+          <t>5132590</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1878732 | Deutsch, DT Automotive Connector Female Blue, Clear, Black, Green, Ora</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Deutsch, DT Automotive Connector Female Blue, Clear, Black, Green, Orange, Brown, Grey 2 Way Crimp Termination DT04-2P</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.432</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1878732</t>
         </is>
       </c>
     </row>

--- a/Python/orders_from_order.xlsx
+++ b/Python/orders_from_order.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,7 +426,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RS Components</t>
+          <t>Conrad</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8496128 | RS PRO France, Germany Mains Plug Black, 16A, Cable Rubber, 250 V, Scr</t>
+          <t xml:space="preserve">2163361-62 | TRU COMPONENTS T1806P023 Keramik-Kondensator SMD 0805 50 V 10 % (L </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RS PRO France, Germany Mains Plug Black, 16A, Cable Rubber, 250 V, Screw</t>
+          <t>TRU COMPONENTS T1806P023 Keramik-Kondensator SMD 0805 50 V 10 % (L x B) 2.0 mm x 1.2 mm 1000 Teile Tape cut</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -475,51 +475,51 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>33.3306</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8496128</t>
+          <t>2163361-62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0425610 | Deutsch, DT Plastic Male 2 Way Wedge Lock for use with Automotive Conn</t>
+          <t xml:space="preserve">2163363-62 | TRU COMPONENTS T1806P026 Keramik-Kondensator SMD 1206 50 V 10 % (L </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deutsch, DT Plastic Male 2 Way Wedge Lock for use with Automotive Connectors</t>
+          <t>TRU COMPONENTS T1806P026 Keramik-Kondensator SMD 1206 50 V 10 % (L x B) 3.2 mm x 1.6 mm 500 Teile Tape cut</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>29.8595</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0425610</t>
+          <t>2163363-62</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5132590 | RS PRO Insulated Crimp Bootlace Ferrule, 8 mm Pin Length, 1.5 mm Pin D</t>
+          <t xml:space="preserve">2163357-62 | TRU COMPONENTS T1806P020 Keramik-Kondensator SMD 0603 50 V 10 % (L </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RS PRO Insulated Crimp Bootlace Ferrule, 8 mm Pin Length, 1.5 mm Pin Diameter, Grey from 18 AWG to 18 AWG Wire Size</t>
+          <t>TRU COMPONENTS T1806P020 Keramik-Kondensator SMD 0603 50 V 10 % (L x B) 1.6 mm x 0.8 mm 1000 Teile Tape cut</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -529,39 +529,174 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>54.1653</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5132590</t>
+          <t>2163357-62</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1878732 | Deutsch, DT Automotive Connector Female Blue, Clear, Black, Green, Ora</t>
+          <t>1564932-62 | TRU COMPONENTS Keramik-Kondensator radial bedrahtet 50 V 20 % 500 S</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deutsch, DT Automotive Connector Female Blue, Clear, Black, Green, Orange, Brown, Grey 2 Way Crimp Termination DT04-2P</t>
+          <t>TRU COMPONENTS Keramik-Kondensator radial bedrahtet 50 V 20 % 500 St.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>29.8595</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1878732</t>
+          <t>1564932-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1564931-62 | TRU COMPONENTS Elektrolyt-Kondensator radial bedrahtet 20 % 148 St.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TRU COMPONENTS Elektrolyt-Kondensator radial bedrahtet 20 % 148 St.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10.4132</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1564931-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>458084-62 | Kemet C0805C106K4PAC7800+ Keramik-Kondensator SMD 0805 10 µF 16 V 10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kemet C0805C106K4PAC7800+ Keramik-Kondensator SMD 0805 10 µF 16 V 10 % 1 St. Tape cut</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.1157</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>458084-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">445372-62 | Yageo CC1206ZPY5V7BB475 Keramik-Kondensator SMD 1206 4.7 µF 16 V 20 </t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Yageo CC1206ZPY5V7BB475 Keramik-Kondensator SMD 1206 4.7 µF 16 V 20 % 1 St. Tape cut</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0248</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>445372-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717352-62 | TRU COMPONENTS TC-6869408 TC-6869408 Sortiments-Album SMD 0603 0.1 </t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TRU COMPONENTS TC-6869408 TC-6869408 Sortiments-Album SMD 0603 0.1 W 1 % 1000 Teile</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>29.8595</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1717352-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1717354-62 | TRU COMPONENTS TC-6869416 TC-6869416 Sortiments-Album SMD 1206 0.25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TRU COMPONENTS TC-6869416 TC-6869416 Sortiments-Album SMD 1206 0.25 W 1 % 1000 Teile</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>41.6612</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1717354-62</t>
         </is>
       </c>
     </row>
